--- a/Assets/Data/Excel/CardData.xlsx
+++ b/Assets/Data/Excel/CardData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="233">
   <si>
     <t>卡牌ID</t>
   </si>
@@ -78,9 +78,6 @@
     <t>词条</t>
   </si>
   <si>
-    <t>牌库</t>
-  </si>
-  <si>
     <t>cardId</t>
   </si>
   <si>
@@ -126,9 +123,6 @@
     <t>destroyEffect</t>
   </si>
   <si>
-    <t>libraries</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -177,9 +171,6 @@
     <t>QuickTurnover|Payoff</t>
   </si>
   <si>
-    <t>1|2</t>
-  </si>
-  <si>
     <t>主播</t>
   </si>
   <si>
@@ -339,9 +330,6 @@
     <t>ReduceMoney;60</t>
   </si>
   <si>
-    <t>0|1|2</t>
-  </si>
-  <si>
     <t>高级教师</t>
   </si>
   <si>
@@ -625,9 +613,6 @@
   </si>
   <si>
     <t>AddMoney;60</t>
-  </si>
-  <si>
-    <t>0|1</t>
   </si>
   <si>
     <t>学生</t>
@@ -930,7 +915,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -970,6 +955,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1335,7 +1326,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="4">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
@@ -1359,16 +1350,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="7">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="8">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="7">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="9">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10">
@@ -1377,89 +1368,89 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="38" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1479,7 +1470,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2123,158 +2117,149 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="2" s="2" customFormat="1" spans="1:17">
       <c r="A2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="3" s="2" customFormat="1" spans="1:17">
       <c r="A3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" s="13" customFormat="1" spans="1:17">
+      <c r="A4" s="13">
+        <v>9999</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="C4" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" s="11" customFormat="1" spans="1:17">
-      <c r="A4" s="11">
-        <v>9999</v>
-      </c>
-      <c r="B4" s="11" t="s">
+      <c r="D4" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="13">
+        <v>1</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="13">
+        <v>200</v>
+      </c>
+      <c r="H4" s="13">
+        <v>0</v>
+      </c>
+      <c r="I4" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="11">
-        <v>1</v>
-      </c>
-      <c r="F4" s="11" t="s">
+      <c r="J4" s="13">
+        <v>0</v>
+      </c>
+      <c r="K4" s="13">
+        <v>0</v>
+      </c>
+      <c r="L4" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="11">
-        <v>200</v>
-      </c>
-      <c r="H4" s="11">
-        <v>0</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="11">
-        <v>0</v>
-      </c>
-      <c r="K4" s="11">
-        <v>0</v>
-      </c>
-      <c r="L4" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>39</v>
+      <c r="N4" s="13" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -2282,19 +2267,19 @@
         <v>1003</v>
       </c>
       <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" t="s">
         <v>42</v>
       </c>
-      <c r="C5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" t="s">
-        <v>44</v>
-      </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G5">
         <v>200</v>
@@ -2303,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="I5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -2312,22 +2297,19 @@
         <v>4</v>
       </c>
       <c r="L5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M5" t="s">
+        <v>44</v>
+      </c>
+      <c r="N5" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" t="s">
+        <v>45</v>
+      </c>
+      <c r="P5" t="s">
         <v>46</v>
-      </c>
-      <c r="N5" t="s">
-        <v>39</v>
-      </c>
-      <c r="O5" t="s">
-        <v>47</v>
-      </c>
-      <c r="P5" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -2335,19 +2317,19 @@
         <v>1006</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G6">
         <v>150</v>
@@ -2356,7 +2338,7 @@
         <v>120</v>
       </c>
       <c r="I6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J6">
         <v>2</v>
@@ -2365,42 +2347,40 @@
         <v>3</v>
       </c>
       <c r="L6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="N6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="P6" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>49</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="Q6" s="14"/>
     </row>
     <row r="7" spans="1:17">
       <c r="A7">
         <v>1007</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G7">
         <v>250</v>
@@ -2409,7 +2389,7 @@
         <v>80</v>
       </c>
       <c r="I7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J7">
         <v>2</v>
@@ -2418,42 +2398,40 @@
         <v>10</v>
       </c>
       <c r="L7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="N7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="P7" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>49</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="Q7" s="14"/>
     </row>
     <row r="8" spans="1:17">
       <c r="A8">
         <v>2002</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E8">
         <v>2</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G8">
         <v>100</v>
@@ -2462,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2471,95 +2449,91 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P8" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>49</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="Q8" s="14"/>
     </row>
     <row r="9" spans="1:17">
       <c r="A9">
         <v>3005</v>
       </c>
       <c r="B9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" t="s">
+        <v>63</v>
+      </c>
+      <c r="N9" t="s">
+        <v>37</v>
+      </c>
+      <c r="O9" t="s">
+        <v>37</v>
+      </c>
+      <c r="P9" t="s">
         <v>64</v>
       </c>
-      <c r="C9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9" t="s">
-        <v>40</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M9" t="s">
-        <v>66</v>
-      </c>
-      <c r="N9" t="s">
-        <v>39</v>
-      </c>
-      <c r="O9" t="s">
-        <v>39</v>
-      </c>
-      <c r="P9" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>49</v>
-      </c>
+      <c r="Q9" s="14"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10">
         <v>1012</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E10">
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G10">
         <v>95</v>
@@ -2568,7 +2542,7 @@
         <v>45</v>
       </c>
       <c r="I10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J10">
         <v>2</v>
@@ -2577,42 +2551,40 @@
         <v>7</v>
       </c>
       <c r="L10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P10" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>49</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="Q10" s="14"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11">
         <v>2010</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E11">
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G11">
         <v>95</v>
@@ -2621,7 +2593,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2630,42 +2602,40 @@
         <v>6</v>
       </c>
       <c r="L11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="O11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P11" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>49</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="Q11" s="14"/>
     </row>
     <row r="12" spans="1:17">
       <c r="A12">
         <v>1018</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E12">
         <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G12">
         <v>70</v>
@@ -2674,7 +2644,7 @@
         <v>32</v>
       </c>
       <c r="I12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -2683,42 +2653,40 @@
         <v>5</v>
       </c>
       <c r="L12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="O12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P12" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>49</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="Q12" s="14"/>
     </row>
     <row r="13" spans="1:17">
       <c r="A13">
         <v>2012</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E13">
         <v>2</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G13">
         <v>110</v>
@@ -2727,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2736,42 +2704,40 @@
         <v>5</v>
       </c>
       <c r="L13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="N13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P13" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>49</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="Q13" s="14"/>
     </row>
     <row r="14" spans="1:17">
       <c r="A14">
         <v>4003</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E14">
         <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G14">
         <v>140</v>
@@ -2780,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2789,42 +2755,40 @@
         <v>4</v>
       </c>
       <c r="L14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="O14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P14" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>49</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="Q14" s="14"/>
     </row>
     <row r="15" spans="1:17">
       <c r="A15">
         <v>1020</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E15">
         <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G15">
         <v>80</v>
@@ -2833,7 +2797,7 @@
         <v>25</v>
       </c>
       <c r="I15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J15">
         <v>2</v>
@@ -2842,42 +2806,40 @@
         <v>3</v>
       </c>
       <c r="L15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N15" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="O15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="P15" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>49</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="Q15" s="14"/>
     </row>
     <row r="16" spans="1:17">
       <c r="A16">
         <v>2013</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E16">
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G16">
         <v>90</v>
@@ -2886,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2895,42 +2857,40 @@
         <v>4</v>
       </c>
       <c r="L16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N16" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P16" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>49</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="Q16" s="14"/>
     </row>
     <row r="17" spans="1:17">
       <c r="A17">
         <v>4004</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G17">
         <v>130</v>
@@ -2939,7 +2899,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2948,42 +2908,40 @@
         <v>3</v>
       </c>
       <c r="L17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N17" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P17" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>49</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="Q17" s="14"/>
     </row>
     <row r="18" spans="1:17">
       <c r="A18">
         <v>1002</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G18">
         <v>120</v>
@@ -2992,7 +2950,7 @@
         <v>60</v>
       </c>
       <c r="I18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J18">
         <v>2</v>
@@ -3001,42 +2959,40 @@
         <v>8</v>
       </c>
       <c r="L18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M18" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="N18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O18" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="P18" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>103</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="Q18" s="14"/>
     </row>
     <row r="19" spans="1:17">
       <c r="A19">
         <v>1004</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G19">
         <v>80</v>
@@ -3045,7 +3001,7 @@
         <v>25</v>
       </c>
       <c r="I19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J19">
         <v>2</v>
@@ -3054,42 +3010,40 @@
         <v>0</v>
       </c>
       <c r="L19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M19" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="N19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O19" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="P19" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>103</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="Q19" s="14"/>
     </row>
     <row r="20" spans="1:17">
       <c r="A20">
         <v>1008</v>
       </c>
       <c r="B20" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G20">
         <v>100</v>
@@ -3098,7 +3052,7 @@
         <v>50</v>
       </c>
       <c r="I20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J20">
         <v>2</v>
@@ -3107,42 +3061,40 @@
         <v>6</v>
       </c>
       <c r="L20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M20" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="N20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O20" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="P20" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>103</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="Q20" s="14"/>
     </row>
     <row r="21" spans="1:17">
       <c r="A21">
         <v>1009</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G21">
         <v>60</v>
@@ -3151,7 +3103,7 @@
         <v>40</v>
       </c>
       <c r="I21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J21">
         <v>2</v>
@@ -3160,42 +3112,40 @@
         <v>6</v>
       </c>
       <c r="L21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M21" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="N21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="P21" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>103</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Q21" s="14"/>
     </row>
     <row r="22" spans="1:17">
       <c r="A22">
         <v>2001</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G22">
         <v>80</v>
@@ -3204,7 +3154,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -3213,42 +3163,40 @@
         <v>5</v>
       </c>
       <c r="L22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N22" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="O22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P22" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>103</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Q22" s="14"/>
     </row>
     <row r="23" spans="1:17">
       <c r="A23">
         <v>2004</v>
       </c>
       <c r="B23" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C23" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G23">
         <v>90</v>
@@ -3257,7 +3205,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3266,42 +3214,40 @@
         <v>6</v>
       </c>
       <c r="L23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N23" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="O23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P23" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>103</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="Q23" s="14"/>
     </row>
     <row r="24" spans="1:17">
       <c r="A24">
         <v>2005</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D24" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G24">
         <v>70</v>
@@ -3310,7 +3256,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3319,42 +3265,40 @@
         <v>7</v>
       </c>
       <c r="L24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N24" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="O24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P24" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>103</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="Q24" s="14"/>
     </row>
     <row r="25" spans="1:17">
       <c r="A25">
         <v>3002</v>
       </c>
       <c r="B25" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C25" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G25">
         <v>50</v>
@@ -3363,7 +3307,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3372,42 +3316,40 @@
         <v>0</v>
       </c>
       <c r="L25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M25" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="N25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P25" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>103</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="Q25" s="14"/>
     </row>
     <row r="26" spans="1:17">
       <c r="A26">
         <v>3003</v>
       </c>
       <c r="B26" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C26" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G26">
         <v>80</v>
@@ -3416,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3425,42 +3367,40 @@
         <v>0</v>
       </c>
       <c r="L26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M26" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P26" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>103</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Q26" s="14"/>
     </row>
     <row r="27" spans="1:17">
       <c r="A27">
         <v>3004</v>
       </c>
       <c r="B27" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C27" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G27">
         <v>60</v>
@@ -3469,7 +3409,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3478,42 +3418,40 @@
         <v>0</v>
       </c>
       <c r="L27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M27" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P27" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>103</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="Q27" s="14"/>
     </row>
     <row r="28" spans="1:17">
       <c r="A28">
         <v>1011</v>
       </c>
       <c r="B28" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C28" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G28">
         <v>70</v>
@@ -3522,7 +3460,7 @@
         <v>35</v>
       </c>
       <c r="I28" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J28">
         <v>2</v>
@@ -3531,42 +3469,40 @@
         <v>6</v>
       </c>
       <c r="L28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O28" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="P28" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>103</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="Q28" s="14"/>
     </row>
     <row r="29" spans="1:17">
       <c r="A29">
         <v>2006</v>
       </c>
       <c r="B29" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C29" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D29" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G29">
         <v>85</v>
@@ -3575,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -3584,42 +3520,40 @@
         <v>5</v>
       </c>
       <c r="L29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N29" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="O29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P29" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>103</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Q29" s="14"/>
     </row>
     <row r="30" spans="1:17">
       <c r="A30">
         <v>4001</v>
       </c>
       <c r="B30" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C30" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G30">
         <v>120</v>
@@ -3628,7 +3562,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -3637,42 +3571,40 @@
         <v>4</v>
       </c>
       <c r="L30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N30" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="O30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P30" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>103</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="Q30" s="14"/>
     </row>
     <row r="31" spans="1:17">
       <c r="A31">
         <v>1014</v>
       </c>
       <c r="B31" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C31" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G31">
         <v>80</v>
@@ -3681,7 +3613,7 @@
         <v>35</v>
       </c>
       <c r="I31" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J31">
         <v>2</v>
@@ -3690,42 +3622,40 @@
         <v>3</v>
       </c>
       <c r="L31" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M31" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N31" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O31" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="P31" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>103</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="Q31" s="14"/>
     </row>
     <row r="32" spans="1:17">
       <c r="A32">
         <v>2007</v>
       </c>
       <c r="B32" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C32" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D32" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G32">
         <v>65</v>
@@ -3734,7 +3664,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -3743,42 +3673,40 @@
         <v>4</v>
       </c>
       <c r="L32" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M32" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N32" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="O32" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P32" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>103</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="Q32" s="14"/>
     </row>
     <row r="33" spans="1:17">
       <c r="A33">
         <v>3007</v>
       </c>
       <c r="B33" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C33" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D33" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G33">
         <v>40</v>
@@ -3787,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -3796,42 +3724,40 @@
         <v>0</v>
       </c>
       <c r="L33" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M33" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="N33" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O33" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P33" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>103</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="Q33" s="14"/>
     </row>
     <row r="34" spans="1:17">
       <c r="A34">
         <v>3008</v>
       </c>
       <c r="B34" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C34" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D34" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E34">
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G34">
         <v>25</v>
@@ -3840,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -3849,42 +3775,40 @@
         <v>0</v>
       </c>
       <c r="L34" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M34" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N34" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O34" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P34" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>103</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="Q34" s="14"/>
     </row>
     <row r="35" spans="1:17">
       <c r="A35">
         <v>1015</v>
       </c>
       <c r="B35" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C35" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D35" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G35">
         <v>60</v>
@@ -3893,7 +3817,7 @@
         <v>30</v>
       </c>
       <c r="I35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J35">
         <v>2</v>
@@ -3902,42 +3826,40 @@
         <v>5</v>
       </c>
       <c r="L35" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M35" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N35" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="O35" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P35" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>103</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="Q35" s="14"/>
     </row>
     <row r="36" spans="1:17">
       <c r="A36">
         <v>2008</v>
       </c>
       <c r="B36" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C36" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D36" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E36">
         <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G36">
         <v>80</v>
@@ -3946,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -3955,42 +3877,40 @@
         <v>5</v>
       </c>
       <c r="L36" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M36" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N36" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O36" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P36" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>103</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="Q36" s="14"/>
     </row>
     <row r="37" spans="1:17">
       <c r="A37">
         <v>2009</v>
       </c>
       <c r="B37" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C37" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D37" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G37">
         <v>70</v>
@@ -3999,7 +3919,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -4008,42 +3928,40 @@
         <v>5</v>
       </c>
       <c r="L37" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M37" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N37" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="O37" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P37" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>103</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="Q37" s="14"/>
     </row>
     <row r="38" spans="1:17">
       <c r="A38">
         <v>3009</v>
       </c>
       <c r="B38" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C38" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D38" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G38">
         <v>55</v>
@@ -4052,7 +3970,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -4061,42 +3979,40 @@
         <v>0</v>
       </c>
       <c r="L38" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M38" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="N38" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O38" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P38" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>103</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="Q38" s="14"/>
     </row>
     <row r="39" spans="1:17">
       <c r="A39">
         <v>2011</v>
       </c>
       <c r="B39" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C39" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D39" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G39">
         <v>70</v>
@@ -4105,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -4114,42 +4030,40 @@
         <v>4</v>
       </c>
       <c r="L39" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M39" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N39" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="O39" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P39" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>103</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="Q39" s="14"/>
     </row>
     <row r="40" spans="1:17">
       <c r="A40">
         <v>4002</v>
       </c>
       <c r="B40" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C40" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D40" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E40">
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G40">
         <v>100</v>
@@ -4158,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -4167,42 +4081,40 @@
         <v>4</v>
       </c>
       <c r="L40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N40" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="O40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P40" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>103</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Q40" s="14"/>
     </row>
     <row r="41" spans="1:17">
       <c r="A41">
         <v>1017</v>
       </c>
       <c r="B41" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C41" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D41" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E41">
         <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G41">
         <v>65</v>
@@ -4211,7 +4123,7 @@
         <v>28</v>
       </c>
       <c r="I41" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J41">
         <v>2</v>
@@ -4220,42 +4132,40 @@
         <v>5</v>
       </c>
       <c r="L41" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M41" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N41" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="O41" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P41" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>103</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="Q41" s="14"/>
     </row>
     <row r="42" spans="1:17">
       <c r="A42">
         <v>3012</v>
       </c>
       <c r="B42" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C42" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D42" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G42">
         <v>80</v>
@@ -4264,7 +4174,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -4273,42 +4183,40 @@
         <v>0</v>
       </c>
       <c r="L42" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M42" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="N42" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O42" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P42" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>103</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Q42" s="14"/>
     </row>
     <row r="43" spans="1:17">
       <c r="A43">
         <v>1019</v>
       </c>
       <c r="B43" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C43" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D43" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G43">
         <v>50</v>
@@ -4317,7 +4225,7 @@
         <v>20</v>
       </c>
       <c r="I43" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J43">
         <v>2</v>
@@ -4326,42 +4234,40 @@
         <v>4</v>
       </c>
       <c r="L43" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M43" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N43" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="O43" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P43" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>103</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="Q43" s="14"/>
     </row>
     <row r="44" spans="1:17">
       <c r="A44">
         <v>3013</v>
       </c>
       <c r="B44" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C44" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D44" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E44">
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G44">
         <v>70</v>
@@ -4370,7 +4276,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -4379,42 +4285,40 @@
         <v>0</v>
       </c>
       <c r="L44" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M44" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="N44" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O44" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P44" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>103</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="Q44" s="14"/>
     </row>
     <row r="45" spans="1:17">
       <c r="A45">
         <v>1001</v>
       </c>
       <c r="B45" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C45" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D45" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E45">
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G45">
         <v>50</v>
@@ -4423,7 +4327,7 @@
         <v>30</v>
       </c>
       <c r="I45" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J45">
         <v>2</v>
@@ -4432,42 +4336,40 @@
         <v>5</v>
       </c>
       <c r="L45" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M45" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N45" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O45" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P45" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>199</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="Q45" s="14"/>
     </row>
     <row r="46" spans="1:17">
       <c r="A46">
         <v>1005</v>
       </c>
       <c r="B46" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C46" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D46" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E46">
         <v>0</v>
       </c>
       <c r="F46" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G46">
         <v>30</v>
@@ -4476,7 +4378,7 @@
         <v>20</v>
       </c>
       <c r="I46" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J46">
         <v>2</v>
@@ -4485,42 +4387,40 @@
         <v>4</v>
       </c>
       <c r="L46" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M46" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="N46" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O46" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="P46" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>199</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="Q46" s="14"/>
     </row>
     <row r="47" spans="1:17">
       <c r="A47">
         <v>1010</v>
       </c>
       <c r="B47" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C47" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D47" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G47">
         <v>40</v>
@@ -4529,7 +4429,7 @@
         <v>35</v>
       </c>
       <c r="I47" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J47">
         <v>2</v>
@@ -4538,42 +4438,40 @@
         <v>3</v>
       </c>
       <c r="L47" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M47" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="N47" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O47" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="P47" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>199</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="Q47" s="14"/>
     </row>
     <row r="48" spans="1:17">
       <c r="A48">
         <v>2003</v>
       </c>
       <c r="B48" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C48" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D48" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G48">
         <v>60</v>
@@ -4582,7 +4480,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -4591,52 +4489,50 @@
         <v>8</v>
       </c>
       <c r="L48" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M48" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N48" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="O48" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P48" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>199</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Q48" s="14"/>
     </row>
     <row r="49" spans="1:17">
       <c r="A49">
         <v>3001</v>
       </c>
       <c r="B49" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C49" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D49" t="s">
+        <v>36</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49" t="s">
+        <v>37</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49" t="s">
         <v>38</v>
       </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-      <c r="F49" t="s">
-        <v>39</v>
-      </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49" t="s">
-        <v>40</v>
-      </c>
       <c r="J49">
         <v>0</v>
       </c>
@@ -4644,42 +4540,40 @@
         <v>0</v>
       </c>
       <c r="L49" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M49" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N49" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O49" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P49" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>199</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="Q49" s="14"/>
     </row>
     <row r="50" spans="1:17">
       <c r="A50">
         <v>3006</v>
       </c>
       <c r="B50" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C50" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D50" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G50">
         <v>40</v>
@@ -4688,7 +4582,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -4697,42 +4591,40 @@
         <v>0</v>
       </c>
       <c r="L50" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M50" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="N50" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O50" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P50" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>199</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="Q50" s="14"/>
     </row>
     <row r="51" spans="1:17">
       <c r="A51">
         <v>1013</v>
       </c>
       <c r="B51" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C51" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D51" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E51">
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G51">
         <v>55</v>
@@ -4741,7 +4633,7 @@
         <v>25</v>
       </c>
       <c r="I51" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J51">
         <v>2</v>
@@ -4750,42 +4642,40 @@
         <v>4</v>
       </c>
       <c r="L51" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M51" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N51" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O51" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="P51" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>199</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="Q51" s="14"/>
     </row>
     <row r="52" spans="1:17">
       <c r="A52">
         <v>1016</v>
       </c>
       <c r="B52" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C52" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D52" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E52">
         <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G52">
         <v>45</v>
@@ -4794,7 +4684,7 @@
         <v>20</v>
       </c>
       <c r="I52" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J52">
         <v>2</v>
@@ -4803,42 +4693,40 @@
         <v>4</v>
       </c>
       <c r="L52" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M52" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N52" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="O52" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P52" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>199</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="Q52" s="14"/>
     </row>
     <row r="53" spans="1:17">
       <c r="A53">
         <v>3010</v>
       </c>
       <c r="B53" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C53" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D53" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E53">
         <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G53">
         <v>20</v>
@@ -4847,7 +4735,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -4856,52 +4744,50 @@
         <v>0</v>
       </c>
       <c r="L53" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M53" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="N53" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O53" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P53" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>199</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="Q53" s="14"/>
     </row>
     <row r="54" spans="1:17">
       <c r="A54">
         <v>3011</v>
       </c>
       <c r="B54" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C54" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D54" t="s">
+        <v>36</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54" t="s">
+        <v>37</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54" t="s">
         <v>38</v>
       </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
-      <c r="F54" t="s">
-        <v>39</v>
-      </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-      <c r="I54" t="s">
-        <v>40</v>
-      </c>
       <c r="J54">
         <v>0</v>
       </c>
@@ -4909,23 +4795,21 @@
         <v>0</v>
       </c>
       <c r="L54" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M54" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N54" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O54" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="P54" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>199</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="Q54" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4936,7 +4820,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F130"/>
+  <dimension ref="A1:F180"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="15.125" customWidth="1"/>
@@ -4948,33 +4832,33 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
@@ -4982,13 +4866,13 @@
     </row>
     <row r="3" s="2" customFormat="1" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -7532,6 +7416,1006 @@
       <c r="F130" s="10">
         <f>_xlfn.XLOOKUP(B130,CardData!$A:$A,CardData!E:E,"None")</f>
         <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131" s="11">
+        <v>3</v>
+      </c>
+      <c r="B131" s="12">
+        <v>1003</v>
+      </c>
+      <c r="C131" s="11">
+        <v>1</v>
+      </c>
+      <c r="D131" s="12"/>
+      <c r="E131" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B131,CardData!A:A,CardData!B:B,"")</f>
+        <v>程序员</v>
+      </c>
+      <c r="F131" s="12">
+        <f>_xlfn.XLOOKUP(B131,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="A132" s="11">
+        <v>3</v>
+      </c>
+      <c r="B132" s="12">
+        <v>1006</v>
+      </c>
+      <c r="C132" s="11">
+        <v>1</v>
+      </c>
+      <c r="D132" s="12"/>
+      <c r="E132" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B132,CardData!A:A,CardData!B:B,"")</f>
+        <v>主播</v>
+      </c>
+      <c r="F132" s="12">
+        <f>_xlfn.XLOOKUP(B132,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" s="11">
+        <v>3</v>
+      </c>
+      <c r="B133" s="12">
+        <v>1007</v>
+      </c>
+      <c r="C133" s="11">
+        <v>1</v>
+      </c>
+      <c r="D133" s="12"/>
+      <c r="E133" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B133,CardData!A:A,CardData!B:B,"")</f>
+        <v>医生</v>
+      </c>
+      <c r="F133" s="12">
+        <f>_xlfn.XLOOKUP(B133,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" s="11">
+        <v>3</v>
+      </c>
+      <c r="B134" s="12">
+        <v>2002</v>
+      </c>
+      <c r="C134" s="11">
+        <v>1</v>
+      </c>
+      <c r="D134" s="12"/>
+      <c r="E134" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B134,CardData!A:A,CardData!B:B,"")</f>
+        <v>双层床</v>
+      </c>
+      <c r="F134" s="12">
+        <f>_xlfn.XLOOKUP(B134,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" s="11">
+        <v>3</v>
+      </c>
+      <c r="B135" s="12">
+        <v>3005</v>
+      </c>
+      <c r="C135" s="11">
+        <v>1</v>
+      </c>
+      <c r="D135" s="12"/>
+      <c r="E135" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B135,CardData!A:A,CardData!B:B,"")</f>
+        <v>应急贷款</v>
+      </c>
+      <c r="F135" s="12">
+        <f>_xlfn.XLOOKUP(B135,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" s="11">
+        <v>3</v>
+      </c>
+      <c r="B136" s="12">
+        <v>1012</v>
+      </c>
+      <c r="C136" s="11">
+        <v>1</v>
+      </c>
+      <c r="D136" s="12"/>
+      <c r="E136" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B136,CardData!A:A,CardData!B:B,"")</f>
+        <v>夜班护士</v>
+      </c>
+      <c r="F136" s="12">
+        <f>_xlfn.XLOOKUP(B136,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" s="11">
+        <v>3</v>
+      </c>
+      <c r="B137" s="12">
+        <v>2010</v>
+      </c>
+      <c r="C137" s="11">
+        <v>1</v>
+      </c>
+      <c r="D137" s="12"/>
+      <c r="E137" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B137,CardData!A:A,CardData!B:B,"")</f>
+        <v>洗衣堆</v>
+      </c>
+      <c r="F137" s="12">
+        <f>_xlfn.XLOOKUP(B137,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" s="11">
+        <v>3</v>
+      </c>
+      <c r="B138" s="12">
+        <v>1018</v>
+      </c>
+      <c r="C138" s="11">
+        <v>1</v>
+      </c>
+      <c r="D138" s="12"/>
+      <c r="E138" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B138,CardData!A:A,CardData!B:B,"")</f>
+        <v>装修负责人</v>
+      </c>
+      <c r="F138" s="12">
+        <f>_xlfn.XLOOKUP(B138,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" s="11">
+        <v>3</v>
+      </c>
+      <c r="B139" s="12">
+        <v>2012</v>
+      </c>
+      <c r="C139" s="11">
+        <v>1</v>
+      </c>
+      <c r="D139" s="12"/>
+      <c r="E139" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B139,CardData!A:A,CardData!B:B,"")</f>
+        <v>隔断墙</v>
+      </c>
+      <c r="F139" s="12">
+        <f>_xlfn.XLOOKUP(B139,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" s="11">
+        <v>3</v>
+      </c>
+      <c r="B140" s="12">
+        <v>4003</v>
+      </c>
+      <c r="C140" s="11">
+        <v>1</v>
+      </c>
+      <c r="D140" s="12"/>
+      <c r="E140" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B140,CardData!A:A,CardData!B:B,"")</f>
+        <v>蓝图交易</v>
+      </c>
+      <c r="F140" s="12">
+        <f>_xlfn.XLOOKUP(B140,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" s="11">
+        <v>3</v>
+      </c>
+      <c r="B141" s="12">
+        <v>1020</v>
+      </c>
+      <c r="C141" s="11">
+        <v>1</v>
+      </c>
+      <c r="D141" s="12"/>
+      <c r="E141" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B141,CardData!A:A,CardData!B:B,"")</f>
+        <v>闪电经纪人</v>
+      </c>
+      <c r="F141" s="12">
+        <f>_xlfn.XLOOKUP(B141,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" s="11">
+        <v>3</v>
+      </c>
+      <c r="B142" s="12">
+        <v>2013</v>
+      </c>
+      <c r="C142" s="11">
+        <v>1</v>
+      </c>
+      <c r="D142" s="12"/>
+      <c r="E142" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B142,CardData!A:A,CardData!B:B,"")</f>
+        <v>涡轮计价表</v>
+      </c>
+      <c r="F142" s="12">
+        <f>_xlfn.XLOOKUP(B142,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143" s="11">
+        <v>3</v>
+      </c>
+      <c r="B143" s="12">
+        <v>4004</v>
+      </c>
+      <c r="C143" s="11">
+        <v>1</v>
+      </c>
+      <c r="D143" s="12"/>
+      <c r="E143" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B143,CardData!A:A,CardData!B:B,"")</f>
+        <v>最终对账</v>
+      </c>
+      <c r="F143" s="12">
+        <f>_xlfn.XLOOKUP(B143,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="A144" s="11">
+        <v>3</v>
+      </c>
+      <c r="B144" s="12">
+        <v>1002</v>
+      </c>
+      <c r="C144" s="11">
+        <v>1</v>
+      </c>
+      <c r="D144" s="12"/>
+      <c r="E144" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B144,CardData!A:A,CardData!B:B,"")</f>
+        <v>白领</v>
+      </c>
+      <c r="F144" s="12">
+        <f>_xlfn.XLOOKUP(B144,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145" s="11">
+        <v>3</v>
+      </c>
+      <c r="B145" s="12">
+        <v>1004</v>
+      </c>
+      <c r="C145" s="11">
+        <v>1</v>
+      </c>
+      <c r="D145" s="12"/>
+      <c r="E145" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B145,CardData!A:A,CardData!B:B,"")</f>
+        <v>高级教师</v>
+      </c>
+      <c r="F145" s="12">
+        <f>_xlfn.XLOOKUP(B145,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146" s="11">
+        <v>3</v>
+      </c>
+      <c r="B146" s="12">
+        <v>1008</v>
+      </c>
+      <c r="C146" s="11">
+        <v>1</v>
+      </c>
+      <c r="D146" s="12"/>
+      <c r="E146" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B146,CardData!A:A,CardData!B:B,"")</f>
+        <v>厨师</v>
+      </c>
+      <c r="F146" s="12">
+        <f>_xlfn.XLOOKUP(B146,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147" s="11">
+        <v>3</v>
+      </c>
+      <c r="B147" s="12">
+        <v>1009</v>
+      </c>
+      <c r="C147" s="11">
+        <v>1</v>
+      </c>
+      <c r="D147" s="12"/>
+      <c r="E147" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B147,CardData!A:A,CardData!B:B,"")</f>
+        <v>画家</v>
+      </c>
+      <c r="F147" s="12">
+        <f>_xlfn.XLOOKUP(B147,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148" s="11">
+        <v>3</v>
+      </c>
+      <c r="B148" s="12">
+        <v>2001</v>
+      </c>
+      <c r="C148" s="11">
+        <v>1</v>
+      </c>
+      <c r="D148" s="12"/>
+      <c r="E148" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B148,CardData!A:A,CardData!B:B,"")</f>
+        <v>空调</v>
+      </c>
+      <c r="F148" s="12">
+        <f>_xlfn.XLOOKUP(B148,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="A149" s="11">
+        <v>3</v>
+      </c>
+      <c r="B149" s="12">
+        <v>2004</v>
+      </c>
+      <c r="C149" s="11">
+        <v>1</v>
+      </c>
+      <c r="D149" s="12"/>
+      <c r="E149" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B149,CardData!A:A,CardData!B:B,"")</f>
+        <v>WiFi路由器</v>
+      </c>
+      <c r="F149" s="12">
+        <f>_xlfn.XLOOKUP(B149,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" s="11">
+        <v>3</v>
+      </c>
+      <c r="B150" s="12">
+        <v>2005</v>
+      </c>
+      <c r="C150" s="11">
+        <v>1</v>
+      </c>
+      <c r="D150" s="12"/>
+      <c r="E150" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B150,CardData!A:A,CardData!B:B,"")</f>
+        <v>洗衣机</v>
+      </c>
+      <c r="F150" s="12">
+        <f>_xlfn.XLOOKUP(B150,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" s="11">
+        <v>3</v>
+      </c>
+      <c r="B151" s="12">
+        <v>3002</v>
+      </c>
+      <c r="C151" s="11">
+        <v>1</v>
+      </c>
+      <c r="D151" s="12"/>
+      <c r="E151" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B151,CardData!A:A,CardData!B:B,"")</f>
+        <v>经纪人介绍</v>
+      </c>
+      <c r="F151" s="12">
+        <f>_xlfn.XLOOKUP(B151,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" s="11">
+        <v>3</v>
+      </c>
+      <c r="B152" s="12">
+        <v>3003</v>
+      </c>
+      <c r="C152" s="11">
+        <v>1</v>
+      </c>
+      <c r="D152" s="12"/>
+      <c r="E152" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B152,CardData!A:A,CardData!B:B,"")</f>
+        <v>续签</v>
+      </c>
+      <c r="F152" s="12">
+        <f>_xlfn.XLOOKUP(B152,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" s="11">
+        <v>3</v>
+      </c>
+      <c r="B153" s="12">
+        <v>3004</v>
+      </c>
+      <c r="C153" s="11">
+        <v>1</v>
+      </c>
+      <c r="D153" s="12"/>
+      <c r="E153" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B153,CardData!A:A,CardData!B:B,"")</f>
+        <v>维修</v>
+      </c>
+      <c r="F153" s="12">
+        <f>_xlfn.XLOOKUP(B153,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" s="11">
+        <v>3</v>
+      </c>
+      <c r="B154" s="12">
+        <v>1011</v>
+      </c>
+      <c r="C154" s="11">
+        <v>1</v>
+      </c>
+      <c r="D154" s="12"/>
+      <c r="E154" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B154,CardData!A:A,CardData!B:B,"")</f>
+        <v>工会文员</v>
+      </c>
+      <c r="F154" s="12">
+        <f>_xlfn.XLOOKUP(B154,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" s="11">
+        <v>3</v>
+      </c>
+      <c r="B155" s="12">
+        <v>2006</v>
+      </c>
+      <c r="C155" s="11">
+        <v>1</v>
+      </c>
+      <c r="D155" s="12"/>
+      <c r="E155" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B155,CardData!A:A,CardData!B:B,"")</f>
+        <v>租赁账本</v>
+      </c>
+      <c r="F155" s="12">
+        <f>_xlfn.XLOOKUP(B155,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" s="11">
+        <v>3</v>
+      </c>
+      <c r="B156" s="12">
+        <v>4001</v>
+      </c>
+      <c r="C156" s="11">
+        <v>1</v>
+      </c>
+      <c r="D156" s="12"/>
+      <c r="E156" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B156,CardData!A:A,CardData!B:B,"")</f>
+        <v>长期租约</v>
+      </c>
+      <c r="F156" s="12">
+        <f>_xlfn.XLOOKUP(B156,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" s="11">
+        <v>3</v>
+      </c>
+      <c r="B157" s="12">
+        <v>1014</v>
+      </c>
+      <c r="C157" s="11">
+        <v>1</v>
+      </c>
+      <c r="D157" s="12"/>
+      <c r="E157" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B157,CardData!A:A,CardData!B:B,"")</f>
+        <v>夜骑手</v>
+      </c>
+      <c r="F157" s="12">
+        <f>_xlfn.XLOOKUP(B157,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" s="11">
+        <v>3</v>
+      </c>
+      <c r="B158" s="12">
+        <v>2007</v>
+      </c>
+      <c r="C158" s="11">
+        <v>1</v>
+      </c>
+      <c r="D158" s="12"/>
+      <c r="E158" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B158,CardData!A:A,CardData!B:B,"")</f>
+        <v>清仓招牌</v>
+      </c>
+      <c r="F158" s="12">
+        <f>_xlfn.XLOOKUP(B158,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" s="11">
+        <v>3</v>
+      </c>
+      <c r="B159" s="12">
+        <v>3007</v>
+      </c>
+      <c r="C159" s="11">
+        <v>1</v>
+      </c>
+      <c r="D159" s="12"/>
+      <c r="E159" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B159,CardData!A:A,CardData!B:B,"")</f>
+        <v>招聘电话</v>
+      </c>
+      <c r="F159" s="12">
+        <f>_xlfn.XLOOKUP(B159,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" s="11">
+        <v>3</v>
+      </c>
+      <c r="B160" s="12">
+        <v>3008</v>
+      </c>
+      <c r="C160" s="11">
+        <v>1</v>
+      </c>
+      <c r="D160" s="12"/>
+      <c r="E160" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B160,CardData!A:A,CardData!B:B,"")</f>
+        <v>搬迁令</v>
+      </c>
+      <c r="F160" s="12">
+        <f>_xlfn.XLOOKUP(B160,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" s="11">
+        <v>3</v>
+      </c>
+      <c r="B161" s="12">
+        <v>1015</v>
+      </c>
+      <c r="C161" s="11">
+        <v>1</v>
+      </c>
+      <c r="D161" s="12"/>
+      <c r="E161" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B161,CardData!A:A,CardData!B:B,"")</f>
+        <v>万能工</v>
+      </c>
+      <c r="F161" s="12">
+        <f>_xlfn.XLOOKUP(B161,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" s="11">
+        <v>3</v>
+      </c>
+      <c r="B162" s="12">
+        <v>2008</v>
+      </c>
+      <c r="C162" s="11">
+        <v>1</v>
+      </c>
+      <c r="D162" s="12"/>
+      <c r="E162" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B162,CardData!A:A,CardData!B:B,"")</f>
+        <v>额外书架</v>
+      </c>
+      <c r="F162" s="12">
+        <f>_xlfn.XLOOKUP(B162,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" s="11">
+        <v>3</v>
+      </c>
+      <c r="B163" s="12">
+        <v>2009</v>
+      </c>
+      <c r="C163" s="11">
+        <v>1</v>
+      </c>
+      <c r="D163" s="12"/>
+      <c r="E163" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B163,CardData!A:A,CardData!B:B,"")</f>
+        <v>电源插座</v>
+      </c>
+      <c r="F163" s="12">
+        <f>_xlfn.XLOOKUP(B163,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" s="11">
+        <v>3</v>
+      </c>
+      <c r="B164" s="12">
+        <v>3009</v>
+      </c>
+      <c r="C164" s="11">
+        <v>1</v>
+      </c>
+      <c r="D164" s="12"/>
+      <c r="E164" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B164,CardData!A:A,CardData!B:B,"")</f>
+        <v>维修队</v>
+      </c>
+      <c r="F164" s="12">
+        <f>_xlfn.XLOOKUP(B164,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" s="11">
+        <v>3</v>
+      </c>
+      <c r="B165" s="12">
+        <v>2011</v>
+      </c>
+      <c r="C165" s="11">
+        <v>1</v>
+      </c>
+      <c r="D165" s="12"/>
+      <c r="E165" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B165,CardData!A:A,CardData!B:B,"")</f>
+        <v>开放屋标志</v>
+      </c>
+      <c r="F165" s="12">
+        <f>_xlfn.XLOOKUP(B165,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
+      <c r="A166" s="11">
+        <v>3</v>
+      </c>
+      <c r="B166" s="12">
+        <v>4002</v>
+      </c>
+      <c r="C166" s="11">
+        <v>1</v>
+      </c>
+      <c r="D166" s="12"/>
+      <c r="E166" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B166,CardData!A:A,CardData!B:B,"")</f>
+        <v>空房条款</v>
+      </c>
+      <c r="F166" s="12">
+        <f>_xlfn.XLOOKUP(B166,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" s="11">
+        <v>3</v>
+      </c>
+      <c r="B167" s="12">
+        <v>1017</v>
+      </c>
+      <c r="C167" s="11">
+        <v>1</v>
+      </c>
+      <c r="D167" s="12"/>
+      <c r="E167" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B167,CardData!A:A,CardData!B:B,"")</f>
+        <v>楼层规划师</v>
+      </c>
+      <c r="F167" s="12">
+        <f>_xlfn.XLOOKUP(B167,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168" s="11">
+        <v>3</v>
+      </c>
+      <c r="B168" s="12">
+        <v>3012</v>
+      </c>
+      <c r="C168" s="11">
+        <v>1</v>
+      </c>
+      <c r="D168" s="12"/>
+      <c r="E168" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B168,CardData!A:A,CardData!B:B,"")</f>
+        <v>施工许可</v>
+      </c>
+      <c r="F168" s="12">
+        <f>_xlfn.XLOOKUP(B168,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" s="11">
+        <v>3</v>
+      </c>
+      <c r="B169" s="12">
+        <v>1019</v>
+      </c>
+      <c r="C169" s="11">
+        <v>1</v>
+      </c>
+      <c r="D169" s="12"/>
+      <c r="E169" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B169,CardData!A:A,CardData!B:B,"")</f>
+        <v>夜间审计员</v>
+      </c>
+      <c r="F169" s="12">
+        <f>_xlfn.XLOOKUP(B169,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170" s="11">
+        <v>3</v>
+      </c>
+      <c r="B170" s="12">
+        <v>3013</v>
+      </c>
+      <c r="C170" s="11">
+        <v>1</v>
+      </c>
+      <c r="D170" s="12"/>
+      <c r="E170" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B170,CardData!A:A,CardData!B:B,"")</f>
+        <v>快速结算</v>
+      </c>
+      <c r="F170" s="12">
+        <f>_xlfn.XLOOKUP(B170,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" s="11">
+        <v>3</v>
+      </c>
+      <c r="B171" s="12">
+        <v>1001</v>
+      </c>
+      <c r="C171" s="11">
+        <v>1</v>
+      </c>
+      <c r="D171" s="12"/>
+      <c r="E171" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B171,CardData!A:A,CardData!B:B,"")</f>
+        <v>工人</v>
+      </c>
+      <c r="F171" s="12">
+        <f>_xlfn.XLOOKUP(B171,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172" s="11">
+        <v>3</v>
+      </c>
+      <c r="B172" s="12">
+        <v>1005</v>
+      </c>
+      <c r="C172" s="11">
+        <v>1</v>
+      </c>
+      <c r="D172" s="12"/>
+      <c r="E172" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B172,CardData!A:A,CardData!B:B,"")</f>
+        <v>学生</v>
+      </c>
+      <c r="F172" s="12">
+        <f>_xlfn.XLOOKUP(B172,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173" s="11">
+        <v>3</v>
+      </c>
+      <c r="B173" s="12">
+        <v>1010</v>
+      </c>
+      <c r="C173" s="11">
+        <v>1</v>
+      </c>
+      <c r="D173" s="12"/>
+      <c r="E173" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B173,CardData!A:A,CardData!B:B,"")</f>
+        <v>快递员</v>
+      </c>
+      <c r="F173" s="12">
+        <f>_xlfn.XLOOKUP(B173,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174" s="11">
+        <v>3</v>
+      </c>
+      <c r="B174" s="12">
+        <v>2003</v>
+      </c>
+      <c r="C174" s="11">
+        <v>1</v>
+      </c>
+      <c r="D174" s="12"/>
+      <c r="E174" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B174,CardData!A:A,CardData!B:B,"")</f>
+        <v>热水器</v>
+      </c>
+      <c r="F174" s="12">
+        <f>_xlfn.XLOOKUP(B174,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" s="11">
+        <v>3</v>
+      </c>
+      <c r="B175" s="12">
+        <v>3001</v>
+      </c>
+      <c r="C175" s="11">
+        <v>1</v>
+      </c>
+      <c r="D175" s="12"/>
+      <c r="E175" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B175,CardData!A:A,CardData!B:B,"")</f>
+        <v>租金奖励</v>
+      </c>
+      <c r="F175" s="12">
+        <f>_xlfn.XLOOKUP(B175,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" s="11">
+        <v>3</v>
+      </c>
+      <c r="B176" s="12">
+        <v>3006</v>
+      </c>
+      <c r="C176" s="11">
+        <v>1</v>
+      </c>
+      <c r="D176" s="12"/>
+      <c r="E176" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B176,CardData!A:A,CardData!B:B,"")</f>
+        <v>催租单</v>
+      </c>
+      <c r="F176" s="12">
+        <f>_xlfn.XLOOKUP(B176,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" s="11">
+        <v>3</v>
+      </c>
+      <c r="B177" s="12">
+        <v>1013</v>
+      </c>
+      <c r="C177" s="11">
+        <v>1</v>
+      </c>
+      <c r="D177" s="12"/>
+      <c r="E177" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B177,CardData!A:A,CardData!B:B,"")</f>
+        <v>临时工</v>
+      </c>
+      <c r="F177" s="12">
+        <f>_xlfn.XLOOKUP(B177,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178" s="11">
+        <v>3</v>
+      </c>
+      <c r="B178" s="12">
+        <v>1016</v>
+      </c>
+      <c r="C178" s="11">
+        <v>1</v>
+      </c>
+      <c r="D178" s="12"/>
+      <c r="E178" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B178,CardData!A:A,CardData!B:B,"")</f>
+        <v>转租户</v>
+      </c>
+      <c r="F178" s="12">
+        <f>_xlfn.XLOOKUP(B178,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" s="11">
+        <v>3</v>
+      </c>
+      <c r="B179" s="12">
+        <v>3010</v>
+      </c>
+      <c r="C179" s="11">
+        <v>1</v>
+      </c>
+      <c r="D179" s="12"/>
+      <c r="E179" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B179,CardData!A:A,CardData!B:B,"")</f>
+        <v>空房清单</v>
+      </c>
+      <c r="F179" s="12">
+        <f>_xlfn.XLOOKUP(B179,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" s="11">
+        <v>3</v>
+      </c>
+      <c r="B180" s="12">
+        <v>3011</v>
+      </c>
+      <c r="C180" s="11">
+        <v>1</v>
+      </c>
+      <c r="D180" s="12"/>
+      <c r="E180" s="12" t="str">
+        <f>_xlfn.XLOOKUP(B180,CardData!A:A,CardData!B:B,"")</f>
+        <v>折扣传单</v>
+      </c>
+      <c r="F180" s="12">
+        <f>_xlfn.XLOOKUP(B180,CardData!$A:$A,CardData!E:E,"None")</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
